--- a/data/obx_xlsx/CONTX.OL.xlsx
+++ b/data/obx_xlsx/CONTX.OL.xlsx
@@ -9976,14 +9976,38 @@
       <c r="O50" s="16">
         <v>0.67</v>
       </c>
-      <c r="P50" s="17"/>
-      <c r="Q50" s="17"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="17"/>
-      <c r="T50" s="17"/>
-      <c r="U50" s="17"/>
-      <c r="V50" s="17"/>
-      <c r="W50" s="17"/>
+      <c r="P50" s="16">
+        <f t="shared" ref="P50:R50" si="1">SUM(P51:P52)</f>
+        <v>1.02</v>
+      </c>
+      <c r="Q50" s="16">
+        <f t="shared" si="1"/>
+        <v>1.19</v>
+      </c>
+      <c r="R50" s="16">
+        <f t="shared" si="1"/>
+        <v>1.17</v>
+      </c>
+      <c r="S50" s="16">
+        <f t="shared" ref="S50:W50" si="2">SUM(S52,S60)</f>
+        <v>1.4</v>
+      </c>
+      <c r="T50" s="16">
+        <f t="shared" si="2"/>
+        <v>1.31</v>
+      </c>
+      <c r="U50" s="16">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+      <c r="V50" s="16">
+        <f t="shared" si="2"/>
+        <v>0.86</v>
+      </c>
+      <c r="W50" s="16">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
